--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_coquimbo.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:25</t>
+    <t xml:space="preserve">2026-09-24 01:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -964,19 +964,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>-0.42</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="20">
@@ -987,19 +987,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.35</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="21">
@@ -1010,19 +1010,19 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.27</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="23">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_coquimbo.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:15</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2021_coquimbo.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
